--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R5e1c95055f864f55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R1511b8806b9f46c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R57d1757964bf436b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Rb100e7ba1235423f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R57d1757964bf436b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Rb100e7ba1235423f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="Reec014e599c84f1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R05e82a35a52d43c8"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="Reec014e599c84f1f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R05e82a35a52d43c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R55f22cfb16fd46e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R0d965c8f1cf647eb"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R55f22cfb16fd46e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R0d965c8f1cf647eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R4f057ec36e644f94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Rca78b56c36064fb9"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R4f057ec36e644f94"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Rca78b56c36064fb9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R01cb1ff1f2544de9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R745a8f9e358f43ac"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R01cb1ff1f2544de9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R745a8f9e358f43ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R2f0eda90a9ae41a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R1497efb8a0b74a5e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R2f0eda90a9ae41a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R1497efb8a0b74a5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R31bbe8cd4ee140d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R287c843c4fe24e43"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R31bbe8cd4ee140d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R287c843c4fe24e43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="Ra75b488800e14562"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Rb01d82c54a494818"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="Ra75b488800e14562"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Rb01d82c54a494818"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R01589425294843ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R439344be17674c44"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R01589425294843ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R439344be17674c44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R6581d233e3e94f08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R8888157ac4594ff5"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R6581d233e3e94f08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R8888157ac4594ff5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R21df82137ff94e89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Rd310830cd49d445f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="R21df82137ff94e89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Rd310830cd49d445f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="Rcf78c1073d3c404e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R472e664770c444ac"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="Rcf78c1073d3c404e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R472e664770c444ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="Ra28a7eb4f1824687"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R814ef7978ea54f14"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="Ra28a7eb4f1824687"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R814ef7978ea54f14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="Re2ce054819a54a73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Rc1f3bd0b44e24900"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/MultipleSheets/output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="Re2ce054819a54a73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="Rc1f3bd0b44e24900"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First" sheetId="1" r:id="Rae464535fa814619"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Second" sheetId="2" r:id="R5eb76ae97ad8402f"/>
   </x:sheets>
 </x:workbook>
 </file>
